--- a/Medición Digital/Archivos Datasphere/Facebook.xlsx
+++ b/Medición Digital/Archivos Datasphere/Facebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\degonzalez\Documents\2026\Backup_2026\Medición Digital\Archivos Datasphere\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A7BD02-2840-4471-8059-A71EBC9AD9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9613613-AA1B-4E7C-8F28-3D754C34FA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="285" windowWidth="20730" windowHeight="11040" xr2:uid="{547126F0-8099-4433-A248-212954CAA8F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{547126F0-8099-4433-A248-212954CAA8F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Facebook" sheetId="1" r:id="rId1"/>
